--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_21_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_21_R3.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1459</v>
+        <v>2.5489</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2264</v>
+        <v>3.4016</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0805</v>
+        <v>-0.8527</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6345</v>
+        <v>4.3224</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5642</v>
+        <v>0.8561</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.1986</v>
+        <v>3.4663</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7331</v>
+        <v>6.7887</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5122</v>
+        <v>1.4788</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2208</v>
+        <v>5.3098</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.3675</v>
+        <v>-2.4663</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.6227</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.4195</v>
+        <v>-1.8435</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9427</v>
+        <v>-0.0571</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2794</v>
+        <v>-0.279</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6633</v>
+        <v>0.2219</v>
       </c>
       <c r="V2" t="n">
-        <v>1.214</v>
+        <v>-0.7886</v>
       </c>
       <c r="W2" t="n">
-        <v>1.214</v>
+        <v>-0.7886</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1113</v>
+        <v>2.5471</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1657</v>
+        <v>4.8293</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0543</v>
+        <v>-2.2822</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3224</v>
+        <v>-0.6345</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8561</v>
+        <v>2.5642</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4663</v>
+        <v>-3.1986</v>
       </c>
       <c r="J3" t="n">
-        <v>6.7887</v>
+        <v>3.7331</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4788</v>
+        <v>3.5122</v>
       </c>
       <c r="L3" t="n">
-        <v>5.3098</v>
+        <v>0.2208</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4663</v>
+        <v>-4.3675</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6227</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8435</v>
+        <v>-3.4195</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4946</v>
+        <v>0.344</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5149</v>
+        <v>-0.1177</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0202</v>
+        <v>0.4617</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7886</v>
+        <v>1.214</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7886</v>
+        <v>1.214</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>T. GINAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1312</v>
+        <v>0.0776</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6365</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7676</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1428</v>
+        <v>-0.1739</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8127</v>
+        <v>1.2413</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.9555</v>
+        <v>-1.4153</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7641</v>
+        <v>0.4836</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2973</v>
+        <v>1.1595</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.5331</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.9069</v>
+        <v>-0.6576</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4845</v>
+        <v>0.0818</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4223</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2926</v>
+        <v>0.4835</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6484</v>
+        <v>-0.1729</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3558</v>
+        <v>0.6563</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6805</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1574</v>
+        <v>0.0613</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0989</v>
+        <v>0.019</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0585</v>
+        <v>0.0423</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3819</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0075</v>
+        <v>0.2113</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1419</v>
+        <v>0.2427</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. GINAT</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3093</v>
+        <v>-0.0058</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8252</v>
+        <v>1.8291</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5159</v>
+        <v>-1.8349</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1739</v>
+        <v>-3.1428</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2413</v>
+        <v>1.8127</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4153</v>
+        <v>-4.9555</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4836</v>
+        <v>0.7641</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1595</v>
+        <v>3.2973</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-2.5331</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6576</v>
+        <v>-3.9069</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0818</v>
+        <v>-1.4845</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-2.4223</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09660000000000001</v>
+        <v>-0.1672</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2908</v>
+        <v>-0.4558</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3875</v>
+        <v>0.2886</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>2.6805</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9077</v>
+        <v>-0.8741</v>
       </c>
       <c r="E7" t="n">
         <v>-1.6676</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7599</v>
+        <v>0.7935</v>
       </c>
       <c r="G7" t="n">
         <v>1.0005</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1428</v>
+        <v>-0.1092</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U7" t="n">
-        <v>0.156</v>
+        <v>0.1896</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9722</v>
+        <v>-1.621</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6002</v>
+        <v>2.3211</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5724</v>
+        <v>-3.9421</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4341</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7481</v>
+        <v>0.0993</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0193</v>
+        <v>-0.2985</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7675</v>
+        <v>0.3978</v>
       </c>
       <c r="V8" t="n">
         <v>-1.214</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5603</v>
+        <v>-3.6104</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9105</v>
+        <v>-2.7925</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6498</v>
+        <v>-0.8179</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0945</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3203</v>
+        <v>0.2702</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7604</v>
+        <v>0.5924</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4665</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4686</v>
+        <v>-4.2931</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6856</v>
+        <v>-1.6109</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.783</v>
+        <v>-2.6821</v>
       </c>
       <c r="G10" t="n">
         <v>-6.0259</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2983</v>
+        <v>-0.1228</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4991</v>
+        <v>-0.4244</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2008</v>
+        <v>0.3016</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3312</v>
+        <v>-7.0377</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.791</v>
+        <v>-3.5983</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5402</v>
+        <v>-3.4394</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0639</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5381</v>
+        <v>-0.2447</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5816</v>
+        <v>-0.389</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0435</v>
+        <v>0.1443</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3943</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.5807</v>
+        <v>-12.2072</v>
       </c>
       <c r="E12" t="n">
-        <v>1.649999999999999</v>
+        <v>2.0236</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.2305</v>
+        <v>-14.2307</v>
       </c>
       <c r="G12" t="n">
         <v>-7.6286</v>
@@ -1390,19 +1390,19 @@
         <v>13.9173</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3337999999999999</v>
+        <v>0.7072999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.163</v>
+        <v>-2.7896</v>
       </c>
       <c r="U12" t="n">
         <v>3.4969</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6467999999999999</v>
+        <v>-0.6467999999999997</v>
       </c>
       <c r="W12" t="n">
-        <v>6.353600000000001</v>
+        <v>6.353599999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-7.000400000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5188</v>
+        <v>3.9158</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9221</v>
+        <v>2.5874</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5967</v>
+        <v>1.3284</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1906</v>
+        <v>0.117</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5185</v>
+        <v>-1.0574</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3279</v>
+        <v>1.1745</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5167</v>
+        <v>2.0651</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3695</v>
+        <v>0.1512</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1472</v>
+        <v>1.9139</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3261</v>
+        <v>-1.9481</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.851</v>
+        <v>-1.2087</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4751</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8556</v>
+        <v>3.2473</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8556</v>
+        <v>3.2473</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3308</v>
+        <v>-0.5208</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2636</v>
+        <v>-0.6917</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0672</v>
+        <v>0.1709</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4947</v>
+        <v>3.3837</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2335</v>
+        <v>2.6862</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2611</v>
+        <v>0.6975</v>
       </c>
       <c r="G14" t="n">
-        <v>0.117</v>
+        <v>1.1906</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0574</v>
+        <v>1.5185</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1745</v>
+        <v>-0.3279</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0651</v>
+        <v>2.5167</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1512</v>
+        <v>2.3695</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9139</v>
+        <v>0.1472</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9481</v>
+        <v>-1.3261</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2087</v>
+        <v>-0.851</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.4751</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2473</v>
+        <v>1.8556</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2473</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9419</v>
+        <v>0.1957</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0455</v>
+        <v>0.0277</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1037</v>
+        <v>0.168</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0619</v>
+        <v>3.3123</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3667</v>
+        <v>2.1466</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.3048</v>
+        <v>1.1657</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5344</v>
+        <v>4.5257</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8618</v>
+        <v>-1.2727</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3962</v>
+        <v>5.7985</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9476</v>
+        <v>5.4982</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2303</v>
+        <v>0.1148</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7173</v>
+        <v>5.3834</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4131</v>
+        <v>-0.9725</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0921</v>
+        <v>-1.3875</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3211</v>
+        <v>0.415</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5996</v>
+        <v>0.57</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4525</v>
+        <v>-0.3183</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1472</v>
+        <v>0.8883</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3584</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.8945</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5095</v>
+        <v>2.876</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7928</v>
+        <v>6.541</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7167</v>
+        <v>-3.665</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5257</v>
+        <v>2.5344</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2727</v>
+        <v>-0.8618</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7985</v>
+        <v>3.3962</v>
       </c>
       <c r="J16" t="n">
-        <v>5.4982</v>
+        <v>4.9476</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1148</v>
+        <v>1.2303</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3834</v>
+        <v>3.7173</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9725</v>
+        <v>-2.4131</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3875</v>
+        <v>-2.0921</v>
       </c>
       <c r="O16" t="n">
-        <v>0.415</v>
+        <v>-0.3211</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2328</v>
+        <v>0.4138</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6721</v>
+        <v>-0.3732</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4393</v>
+        <v>0.787</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5361</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6778999999999999</v>
+        <v>3.3584</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>-3.8945</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.468</v>
+        <v>2.6653</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3706</v>
+        <v>1.4885</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0975</v>
+        <v>1.1768</v>
       </c>
       <c r="G17" t="n">
         <v>4.2802</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0435</v>
+        <v>0.2407</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8962</v>
+        <v>-0.7782</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9397</v>
+        <v>1.019</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3209</v>
+        <v>2.4674</v>
       </c>
       <c r="E18" t="n">
         <v>1.2405</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0803</v>
+        <v>1.2268</v>
       </c>
       <c r="G18" t="n">
         <v>0.8579</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0215</v>
+        <v>0.125</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1845</v>
       </c>
       <c r="U18" t="n">
-        <v>0.163</v>
+        <v>0.3095</v>
       </c>
       <c r="V18" t="n">
         <v>0.7886</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7776999999999999</v>
+        <v>1.0307</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2368</v>
+        <v>0.117</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0145</v>
+        <v>0.9137</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9360000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1419</v>
+        <v>0.1111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0536</v>
+        <v>0.772</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2407</v>
+        <v>0.1131</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1871</v>
+        <v>0.6589</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8781</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7117</v>
+        <v>0.114</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4086</v>
+        <v>0.8804</v>
       </c>
       <c r="V20" t="n">
         <v>1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4199</v>
+        <v>-1.5772</v>
       </c>
       <c r="E21" t="n">
-        <v>1.428</v>
+        <v>0.9562</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8479</v>
+        <v>-2.5334</v>
       </c>
       <c r="G21" t="n">
         <v>1.0081</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6959</v>
+        <v>0.5386</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1889</v>
+        <v>-0.2829</v>
       </c>
       <c r="U21" t="n">
-        <v>0.507</v>
+        <v>0.8215</v>
       </c>
       <c r="V21" t="n">
         <v>-2.428</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0974</v>
+        <v>-3.9065</v>
       </c>
       <c r="E22" t="n">
         <v>-4.1821</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0847</v>
+        <v>0.2755</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0713</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0461</v>
+        <v>0.237</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0351</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0813</v>
+        <v>0.2721</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.5806</v>
+        <v>14.9395</v>
       </c>
       <c r="E23" t="n">
-        <v>13.6946</v>
+        <v>13.6944</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1141</v>
+        <v>1.2449</v>
       </c>
       <c r="G23" t="n">
         <v>7.628500000000002</v>
@@ -2248,13 +2248,13 @@
         <v>18.5561</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3338999999999999</v>
+        <v>2.0251</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.4967</v>
+        <v>-3.4968</v>
       </c>
       <c r="U23" t="n">
-        <v>3.163200000000001</v>
+        <v>5.5221</v>
       </c>
       <c r="V23" t="n">
         <v>0.6467999999999998</v>
